--- a/Uber_Equity_Research_Valuation_Model.xlsx
+++ b/Uber_Equity_Research_Valuation_Model.xlsx
@@ -416,7 +416,7 @@
   <x:sheetData>
     <x:row r="1" ht="23" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>UBER | OVERVIEW</x:v>
+        <x:v>UBER VALUATION OVERVIEW</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -438,7 +438,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="9" t="str">
-        <x:v>PROJECT SNAPSHOT</x:v>
+        <x:v>VALUATION SUMMARY</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
         <x:v>AS OF 22 OCTOBER 2026</x:v>
@@ -502,7 +502,7 @@
         <x:v>Analyst stance</x:v>
       </x:c>
       <x:c r="B12" t="str">
-        <x:v>WATCHLIST / NOT YET A COMPELLING MARGIN OF SAFETY</x:v>
+        <x:v>WATCHLIST: INSUFFICIENT MARGIN OF SAFETY</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -558,7 +558,7 @@
     </x:row>
     <x:row r="21" ht="23" customHeight="1">
       <x:c r="A21" s="23" t="str">
-        <x:v>PROPOSED INVESTMENT DEBATE</x:v>
+        <x:v>INVESTMENT THESIS</x:v>
       </x:c>
       <x:c r="B21" s="23"/>
       <x:c r="C21" s="23"/>
@@ -570,47 +570,47 @@
     </x:row>
     <x:row r="23" ht="45" customHeight="1">
       <x:c r="A23" t="str">
-        <x:v>Debate</x:v>
+        <x:v>Core question</x:v>
       </x:c>
       <x:c r="B23" s="26" t="str">
-        <x:v>Can expanding trips/booking monetization produce attractive unlevered cash flow after the Delivery Hero deal and AV reinvestment?</x:v>
+        <x:v>Can trip growth and better monetization support attractive unlevered cash flow after Delivery Hero financing and AV investment?</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="45" customHeight="1">
       <x:c r="A24" t="str">
-        <x:v>Why not blindly BUY</x:v>
+        <x:v>Why I remain on watchlist</x:v>
       </x:c>
       <x:c r="B24" s="26" t="str">
-        <x:v>DCF is terminal-value heavy and does not fully underwrite Delivery Hero financing nor AV capital intensity.</x:v>
+        <x:v>Terminal value drives much of the DCF. Delivery Hero financing and AV capital needs are not fully modeled.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="45" customHeight="1">
       <x:c r="A25" t="str">
-        <x:v>Bull trigger</x:v>
+        <x:v>Bull-case support</x:v>
       </x:c>
       <x:c r="B25" s="26" t="str">
-        <x:v>Conviction improves if margin gains persist and AV aggregation remains capital-efficient.</x:v>
+        <x:v>Persistent margin gains and AV growth with limited capital investment would support the bull case.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="45" customHeight="1">
       <x:c r="A26" t="str">
-        <x:v>Bear trigger</x:v>
+        <x:v>Bear-case risks</x:v>
       </x:c>
       <x:c r="B26" s="26" t="str">
-        <x:v>Uber owns more robotaxi assets, takes more leverage, or loses access to third-party AV fleet volume.</x:v>
+        <x:v>Greater robotaxi ownership, more debt, or reduced access to third-party AV fleets would weaken the case.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="45" customHeight="1">
       <x:c r="A27" t="str">
-        <x:v>Portfolio statement</x:v>
+        <x:v>Research status</x:v>
       </x:c>
       <x:c r="B27" s="26" t="str">
-        <x:v>Independent research case study; scenario assumptions explicitly marked as analyst estimates.</x:v>
+        <x:v>This independent research case uses analyst estimates for all scenarios.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="23" customHeight="1">
       <x:c r="A30" s="23" t="str">
-        <x:v>NAVIGATION / MODEL FLOW</x:v>
+        <x:v>MODEL GUIDE</x:v>
       </x:c>
       <x:c r="B30" s="23"/>
       <x:c r="C30" s="23"/>
@@ -641,7 +641,7 @@
         <x:v>DCF &amp; Cases / Sensitivity</x:v>
       </x:c>
       <x:c r="B34" t="str">
-        <x:v>Enterprise-to-equity valuation and WACC × g stress test</x:v>
+        <x:v>Enterprise-to-equity valuation and WACC / terminal-growth sensitivity</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="26" customHeight="1">
@@ -649,7 +649,7 @@
         <x:v>Trading Comps</x:v>
       </x:c>
       <x:c r="B35" t="str">
-        <x:v>Lyft and DoorDash observed public valuation anchor (FY2025 EBITDA basis)</x:v>
+        <x:v>Lyft and DoorDash valuation comparison using FY2025 EBITDA</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="26" customHeight="1">
@@ -657,7 +657,7 @@
         <x:v>Deal &amp; Risks / Sources</x:v>
       </x:c>
       <x:c r="B36" t="str">
-        <x:v>Live transaction/AV risks and all input references</x:v>
+        <x:v>Pending transaction and AV risks; source references</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -691,7 +691,7 @@
   <x:sheetData>
     <x:row r="1" ht="23" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>UBER | TRADING COMPS</x:v>
+        <x:v>UBER TRADING COMPARABLES</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -910,7 +910,7 @@
     </x:row>
     <x:row r="19" ht="23" customHeight="1">
       <x:c r="A19" s="23" t="str">
-        <x:v>COMPARABILITY WARNINGS</x:v>
+        <x:v>COMPARABILITY NOTES</x:v>
       </x:c>
       <x:c r="B19" s="23"/>
       <x:c r="C19" s="23"/>
@@ -937,7 +937,7 @@
         <x:v>EBITDA definitions</x:v>
       </x:c>
       <x:c r="B23" s="26" t="str">
-        <x:v>Company-specific adjusted EBITDA definitions differ; isolate accounting / SBC differences.</x:v>
+        <x:v>Adjusted EBITDA definitions differ by company, including accounting and SBC treatment.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="29" customHeight="1">
@@ -950,10 +950,10 @@
     </x:row>
     <x:row r="25" ht="29" customHeight="1">
       <x:c r="A25" t="str">
-        <x:v>Market comp signal</x:v>
+        <x:v>Use of comps</x:v>
       </x:c>
       <x:c r="B25" s="26" t="str">
-        <x:v>A valuation range / sanity-check rather than an independent price target.</x:v>
+        <x:v>Valuation cross-check, not an independent price target.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="29" customHeight="1">
@@ -961,7 +961,7 @@
         <x:v>Uber investment addback</x:v>
       </x:c>
       <x:c r="B26" s="26" t="str">
-        <x:v>Uber financial investments include sizable equity marks and DH stake; normalization differs from peers.</x:v>
+        <x:v>Uber's financial investments include substantial equity marks and a Delivery Hero stake, which differ from peers.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -994,7 +994,7 @@
   <x:sheetData>
     <x:row r="1" ht="23" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>UBER | DEAL &amp; RISKS</x:v>
+        <x:v>UBER TRANSACTION AND RISKS</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -1130,7 +1130,7 @@
         <x:v>As-of state</x:v>
       </x:c>
       <x:c r="B14" t="str">
-        <x:v>Pending; do not assume consummation</x:v>
+        <x:v>Pending as of October 22, 2026</x:v>
       </x:c>
       <x:c r="C14" t="str">
         <x:v>UBER_OFFER_UPDATE</x:v>
@@ -1138,7 +1138,7 @@
     </x:row>
     <x:row r="17" ht="23" customHeight="1">
       <x:c r="A17" s="23" t="str">
-        <x:v>WHAT IS AND IS NOT IN OUR UNDERWRITING</x:v>
+        <x:v>MODEL SCOPE</x:v>
       </x:c>
       <x:c r="B17" s="23"/>
       <x:c r="C17" s="23"/>
@@ -1153,7 +1153,7 @@
         <x:v>Standalone operating case</x:v>
       </x:c>
       <x:c r="B19" s="26" t="str">
-        <x:v>DCF forecasts Uber legacy operations; not a Delivery Hero consolidated three-statement model.</x:v>
+        <x:v>The DCF forecasts Uber's existing operations. Delivery Hero is not consolidated.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="34" customHeight="1">
@@ -1174,7 +1174,7 @@
     </x:row>
     <x:row r="22" ht="34" customHeight="1">
       <x:c r="A22" t="str">
-        <x:v>What a true merger model would require</x:v>
+        <x:v>Merger-model inputs needed</x:v>
       </x:c>
       <x:c r="B22" s="26" t="str">
         <x:v>DH audited segment profits, retention, capex, debt, debt coupon, purchase price allocation, divestiture economics.</x:v>
@@ -1190,7 +1190,7 @@
     </x:row>
     <x:row r="24" ht="34" customHeight="1">
       <x:c r="A24" t="str">
-        <x:v>Near-term validation</x:v>
+        <x:v>Upcoming events</x:v>
       </x:c>
       <x:c r="B24" s="26" t="str">
         <x:v>Nov 4 Q3 earnings; Nov 5 original DH offer acceptance period ends.</x:v>
@@ -1198,7 +1198,7 @@
     </x:row>
     <x:row r="27" ht="23" customHeight="1">
       <x:c r="A27" s="23" t="str">
-        <x:v>INVESTMENT THESIS | FALSIFIABLE MONITORING CHECKLIST</x:v>
+        <x:v>INVESTMENT MONITORING</x:v>
       </x:c>
       <x:c r="B27" s="23"/>
       <x:c r="C27" s="23"/>
@@ -1249,7 +1249,7 @@
         <x:v>AV asset ownership/investment cash uses</x:v>
       </x:c>
       <x:c r="C32" s="26" t="str">
-        <x:v>AV capex far exceeds our sub-1% revenue capex proxy</x:v>
+        <x:v>AV capex substantially exceeds the model's capex assumption of less than 1% of revenue</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="31" customHeight="1">
@@ -1328,7 +1328,7 @@
   <x:sheetData>
     <x:row r="1" ht="23" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>UBER | SOURCES</x:v>
+        <x:v>UBER SOURCES</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -1526,7 +1526,7 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="str">
-        <x:v>Note: URLs in this worksheet are the audit trail for historical inputs; yellow cells are analyst assumptions.</x:v>
+        <x:v>Source URLs document historical inputs. Yellow cells identify analyst assumptions.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1558,7 +1558,7 @@
   <x:sheetData>
     <x:row r="1" ht="23" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>UBER | HISTORICAL</x:v>
+        <x:v>UBER HISTORICAL FINANCIALS</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -1861,12 +1861,12 @@
         <x:v>0.24515401549999105</x:v>
       </x:c>
       <x:c r="F17" s="20" t="str">
-        <x:v>Calculated: NOT fee take rate, accounting presentation varies</x:v>
+        <x:v>Calculated; not a fee take rate. Accounting varies.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="23" customHeight="1">
       <x:c r="A20" s="23" t="str">
-        <x:v>IMPORTANT COMPARABILITY / CASH-FLOW NOTES</x:v>
+        <x:v>COMPARABILITY AND CASH FLOW</x:v>
       </x:c>
       <x:c r="B20" s="23"/>
       <x:c r="C20" s="23"/>
@@ -1879,7 +1879,7 @@
         <x:v>H1 2026 is a six-month period</x:v>
       </x:c>
       <x:c r="B22" s="26" t="str">
-        <x:v>Do not compare directly with 12-month annual results.</x:v>
+        <x:v>H1 covers six months; annual periods cover 12 months.</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1887,7 +1887,7 @@
         <x:v>2024–25 GAAP net income</x:v>
       </x:c>
       <x:c r="B23" s="26" t="str">
-        <x:v>Includes $6.4B / $5.0B tax allowance release respectively; not normalized earnings.</x:v>
+        <x:v>Includes tax allowance releases of $6.4bn and $5.0bn, respectively; not normalized earnings.</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1903,12 +1903,12 @@
         <x:v>2026 UK mobility reclassification</x:v>
       </x:c>
       <x:c r="B25" s="26" t="str">
-        <x:v>Causes reported revenue growth to lag gross bookings; do not interpret revenue/bookings as a pure economic take rate.</x:v>
+        <x:v>UK presentation changes cause revenue growth to lag bookings. Revenue/bookings is not an economic fee rate.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="23" customHeight="1">
       <x:c r="A28" s="23" t="str">
-        <x:v>SEGMENT SNAPSHOT | 2025 FY AND H1 2026 ($mm)</x:v>
+        <x:v>SEGMENT RESULTS (FY2025 AND H1 2026; $mm)</x:v>
       </x:c>
       <x:c r="B28" s="23"/>
       <x:c r="C28" s="23"/>
@@ -2017,7 +2017,7 @@
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="str">
-        <x:v>Mobility segment profit [NON-COMPARABLE]</x:v>
+        <x:v>Mobility segment profit*</x:v>
       </x:c>
       <x:c r="B38" s="14" t="n">
         <x:v>7899</x:v>
@@ -2028,7 +2028,7 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="str">
-        <x:v>Delivery segment profit [NON-COMPARABLE]</x:v>
+        <x:v>Delivery segment profit*</x:v>
       </x:c>
       <x:c r="B39" s="14" t="n">
         <x:v>3572</x:v>
@@ -2039,7 +2039,7 @@
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="36" t="str">
-        <x:v>FY2025 segment profit = Adjusted EBITDA; H1 2026 = Segment Operating Income (new definition).</x:v>
+        <x:v>*FY2025 uses Adjusted EBITDA; H1 2026 uses the new Segment Operating Income definition.</x:v>
       </x:c>
       <x:c r="B41" s="36"/>
       <x:c r="C41" s="36"/>
@@ -2049,7 +2049,7 @@
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="36" t="str">
-        <x:v>DO NOT compare segment profitability across these two definitions without reconciliation.</x:v>
+        <x:v>Reconcile the definitions before comparing segment profitability.</x:v>
       </x:c>
       <x:c r="B42" s="36"/>
       <x:c r="C42" s="36"/>
@@ -2088,7 +2088,7 @@
   <x:sheetData>
     <x:row r="1" ht="23" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>UBER | ASSUMPTIONS</x:v>
+        <x:v>UBER VALUATION ASSUMPTIONS</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -2265,7 +2265,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
-        <x:v>Proportion of FY2026 remaining after reference date</x:v>
+        <x:v>Remaining FY2026 cash flow fraction</x:v>
       </x:c>
       <x:c r="B18" s="34" t="n">
         <x:v>0.25</x:v>
@@ -2287,7 +2287,7 @@
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
       <x:c r="A22" s="23" t="str">
-        <x:v>BEAR / BASE / BULL FORECAST DRIVER ASSUMPTIONS</x:v>
+        <x:v>BEAR, BASE AND BULL FORECAST ASSUMPTIONS</x:v>
       </x:c>
       <x:c r="B22" s="23"/>
       <x:c r="C22" s="23"/>
@@ -2611,17 +2611,17 @@
     </x:row>
     <x:row r="63">
       <x:c r="A63" t="str">
-        <x:v>Model caveat: these forward drivers are original analyst scenarios, not management guidance or consensus estimates.</x:v>
+        <x:v>These forecasts are analyst scenarios, not management guidance or consensus estimates.</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" t="str">
-        <x:v>Revenue/bookings ratio reflects GAAP presentation (incl. UK changes), not a clean economic fee take rate.</x:v>
+        <x:v>Revenue/bookings reflects GAAP presentation, including UK changes. It is not an economic fee take rate.</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" t="str">
-        <x:v>M&amp;A overlay is an explicitly un-underwritten scenario assumption, not a forecast of Delivery Hero deal NPV.</x:v>
+        <x:v>Delivery Hero net-value overlays are scenario assumptions without a full merger model.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2655,7 +2655,7 @@
   <x:sheetData>
     <x:row r="1" ht="23" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>UBER | FORECAST BASE</x:v>
+        <x:v>UBER BASE FORECAST</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -3246,17 +3246,17 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="str">
-        <x:v>Caution: full-year 2026 cash flow is multiplied by the unelapsed Q4 fraction; simplistic partial-year convention.</x:v>
+        <x:v>Only the remaining Q4 share of full-year 2026 cash flow is included, using a simplified timing convention.</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="str">
-        <x:v>Normalized unlevered FCF ≠ company-reported FCF: excludes financing, isolates EBIT after tax, does not add back SBC.</x:v>
+        <x:v>DCF cash flow starts from EBIT after tax, excludes financing and does not add back SBC. It differs from reported FCF.</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="str">
-        <x:v>No Delivery Hero consolidation is assumed; the deal is treated as a separate uncertain valuation overlay.</x:v>
+        <x:v>Delivery Hero is not consolidated. Its uncertain net value appears as a separate valuation overlay.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3290,7 +3290,7 @@
   <x:sheetData>
     <x:row r="1" ht="23" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>UBER | FORECAST BEAR</x:v>
+        <x:v>UBER BEAR FORECAST</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -3881,17 +3881,17 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="str">
-        <x:v>Caution: full-year 2026 cash flow is multiplied by the unelapsed Q4 fraction; simplistic partial-year convention.</x:v>
+        <x:v>Only the remaining Q4 share of full-year 2026 cash flow is included, using a simplified timing convention.</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="str">
-        <x:v>Normalized unlevered FCF ≠ company-reported FCF: excludes financing, isolates EBIT after tax, does not add back SBC.</x:v>
+        <x:v>DCF cash flow starts from EBIT after tax, excludes financing and does not add back SBC. It differs from reported FCF.</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="str">
-        <x:v>No Delivery Hero consolidation is assumed; the deal is treated as a separate uncertain valuation overlay.</x:v>
+        <x:v>Delivery Hero is not consolidated. Its uncertain net value appears as a separate valuation overlay.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3925,7 +3925,7 @@
   <x:sheetData>
     <x:row r="1" ht="23" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>UBER | FORECAST BULL</x:v>
+        <x:v>UBER BULL FORECAST</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -4516,17 +4516,17 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="str">
-        <x:v>Caution: full-year 2026 cash flow is multiplied by the unelapsed Q4 fraction; simplistic partial-year convention.</x:v>
+        <x:v>Only the remaining Q4 share of full-year 2026 cash flow is included, using a simplified timing convention.</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="str">
-        <x:v>Normalized unlevered FCF ≠ company-reported FCF: excludes financing, isolates EBIT after tax, does not add back SBC.</x:v>
+        <x:v>DCF cash flow starts from EBIT after tax, excludes financing and does not add back SBC. It differs from reported FCF.</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="str">
-        <x:v>No Delivery Hero consolidation is assumed; the deal is treated as a separate uncertain valuation overlay.</x:v>
+        <x:v>Delivery Hero is not consolidated. Its uncertain net value appears as a separate valuation overlay.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4560,7 +4560,7 @@
   <x:sheetData>
     <x:row r="1" ht="23" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>UBER | DCF &amp; CASES</x:v>
+        <x:v>UBER DCF VALUATION</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -4851,7 +4851,7 @@
     </x:row>
     <x:row r="21" ht="35" customHeight="1">
       <x:c r="A21" s="26" t="str">
-        <x:v>*Financial investments are separately added at Q2 2026 carrying value. Delivery Hero equity-method stake may be rolled/remeasured on acquisition.</x:v>
+        <x:v>Financial investments use Q2 2026 carrying values. The Delivery Hero stake may be rolled over or remeasured at closing.</x:v>
       </x:c>
       <x:c r="B21" s="26"/>
       <x:c r="C21" s="26"/>
@@ -4859,7 +4859,7 @@
     </x:row>
     <x:row r="22" ht="35" customHeight="1">
       <x:c r="A22" s="26" t="str">
-        <x:v>The proposed Delivery Hero offer is NOT in the standalone UFCF forecast. Case overlays (-$5B/0/+$5B) are illustrative un-underwritten net NPVs.</x:v>
+        <x:v>Delivery Hero is excluded from standalone UFCF. The -$5bn / $0 / +$5bn overlays are illustrative, without a full merger model.</x:v>
       </x:c>
       <x:c r="B22" s="26"/>
       <x:c r="C22" s="26"/>
@@ -4867,7 +4867,7 @@
     </x:row>
     <x:row r="23" ht="35" customHeight="1">
       <x:c r="A23" s="26" t="str">
-        <x:v>Implied values and ranking are extremely sensitive to WACC / terminal growth and unrealized equity investment carrying values.</x:v>
+        <x:v>Valuations depend heavily on WACC, terminal growth and financial investment carrying values.</x:v>
       </x:c>
       <x:c r="B23" s="26"/>
       <x:c r="C23" s="26"/>
@@ -4875,7 +4875,7 @@
     </x:row>
     <x:row r="24" ht="35" customHeight="1">
       <x:c r="A24" s="26" t="str">
-        <x:v>The 2.5% diluted-share cushion and Q4 cash flow fraction are analyst approximations, not latest fully diluted share guidance.</x:v>
+        <x:v>The 2.5% dilution cushion and Q4 cash flow fraction are analyst approximations, not company guidance.</x:v>
       </x:c>
       <x:c r="B24" s="26"/>
       <x:c r="C24" s="26"/>
@@ -4883,7 +4883,7 @@
     </x:row>
     <x:row r="27" ht="23" customHeight="1">
       <x:c r="A27" s="23" t="str">
-        <x:v>UPSIDE DEPENDENCE &amp; THESIS VALIDATION</x:v>
+        <x:v>THESIS AND RISKS</x:v>
       </x:c>
       <x:c r="B27" s="23"/>
       <x:c r="C27" s="23"/>
@@ -4891,26 +4891,26 @@
     </x:row>
     <x:row r="29" ht="32" customHeight="1">
       <x:c r="A29" t="str">
-        <x:v>Core dislocation</x:v>
+        <x:v>Potential mispricing</x:v>
       </x:c>
       <x:c r="B29" s="26" t="str">
-        <x:v>Market may be discounting asset-intensity from AV investment and €-denominated acquisition funding.</x:v>
+        <x:v>The price may reflect higher capital needs from AV investment and euro-denominated acquisition funding.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="32" customHeight="1">
       <x:c r="A30" t="str">
-        <x:v>What validates bull case</x:v>
+        <x:v>Bull-case support</x:v>
       </x:c>
       <x:c r="B30" s="26" t="str">
-        <x:v>Bookings &gt;~20%, scalable GAAP operating margin, AV platform monetization without major capex.</x:v>
+        <x:v>Bookings growth above about 20%, rising GAAP margins and AV monetization without major capex.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="32" customHeight="1">
       <x:c r="A31" t="str">
-        <x:v>What validates bear case</x:v>
+        <x:v>Bear-case risks</x:v>
       </x:c>
       <x:c r="B31" s="26" t="str">
-        <x:v>Slower bookings, elevated driver incentives/insurance, AV bypass, Delivery Hero integration costs.</x:v>
+        <x:v>Slower bookings, higher driver incentives or insurance costs, AV bypass and Delivery Hero integration costs.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="32" customHeight="1">
@@ -4923,10 +4923,10 @@
     </x:row>
     <x:row r="33" ht="32" customHeight="1">
       <x:c r="A33" t="str">
-        <x:v>Do not imply company guidance</x:v>
+        <x:v>Forecast basis</x:v>
       </x:c>
       <x:c r="B33" s="26" t="str">
-        <x:v>All scenario forecasts and fair values are analyst work.</x:v>
+        <x:v>All scenario forecasts and fair values are my estimates.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4959,7 +4959,7 @@
   <x:sheetData>
     <x:row r="1" ht="23" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>UBER | SENSITIVITY</x:v>
+        <x:v>UBER VALUATION SENSITIVITY</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -5312,12 +5312,12 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="str">
-        <x:v>Important: table holds the Base operating forecast and net financial investments constant. It changes WACC and terminal g only.</x:v>
+        <x:v>The table changes WACC and terminal growth only. Base operating forecasts and net financial investments stay fixed.</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="str">
-        <x:v>Terminal value dominates DCF. A seemingly precise price target should not be presented as certainty.</x:v>
+        <x:v>Terminal value accounts for much of the DCF. The price estimate is sensitive to long-term assumptions.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
